--- a/artfynd/A 63699-2025 artfynd.xlsx
+++ b/artfynd/A 63699-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67991210</v>
+        <v>67991203</v>
       </c>
       <c r="B2" t="n">
-        <v>84795</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>236437</v>
+        <v>3611</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stålkvarnebäcken väster om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>425313.0615157315</v>
+        <v>425298</v>
       </c>
       <c r="R2" t="n">
-        <v>6482377.911381242</v>
+        <v>6482435</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +752,9 @@
           <t>2017-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67991196</v>
+        <v>67991200</v>
       </c>
       <c r="B3" t="n">
-        <v>84795</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>236437</v>
+        <v>4405</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>425303.7528397053</v>
+        <v>425279</v>
       </c>
       <c r="R3" t="n">
-        <v>6482329.440644748</v>
+        <v>6482391</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +854,9 @@
           <t>2017-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,53 +888,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67991200</v>
+        <v>69847128</v>
       </c>
       <c r="B4" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4405</v>
+        <v>221317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stålkvarnebäcken väster om, Vg</t>
+          <t>Lerdala k:a sydost, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>425278.7254509574</v>
+        <v>425301</v>
       </c>
       <c r="R4" t="n">
-        <v>6482391.120083758</v>
+        <v>6482359</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,27 +953,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-09-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kalkgranskog av högsta klass</t>
+          <t>väg, sydvänd grusgropskant</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,27 +978,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67991203</v>
+        <v>69847108</v>
       </c>
       <c r="B5" t="n">
-        <v>85187</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,46 +1005,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3611</v>
+        <v>222133</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stålkvarnebäcken väster om, Vg</t>
+          <t>Lerdala k:a sydost, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>425298.4218204728</v>
+        <v>425301</v>
       </c>
       <c r="R5" t="n">
-        <v>6482434.684225057</v>
+        <v>6482359</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,27 +1059,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-09-26</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kalkgranskog av högsta klass</t>
+          <t>väg, sydvänd grusgropskant</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,65 +1084,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69847128</v>
+        <v>67991196</v>
       </c>
       <c r="B6" t="n">
-        <v>101358</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89870</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221317</v>
+        <v>236437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lerdala k:a sydost, Vg</t>
+          <t>Stålkvarnebäcken väster om, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>425301</v>
+        <v>425304</v>
       </c>
       <c r="R6" t="n">
-        <v>6482359</v>
+        <v>6482329</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,17 +1165,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2000-07-14</t>
+          <t>2017-09-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2000-07-14</t>
+          <t>2017-09-26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>väg, sydvänd grusgropskant</t>
+          <t>Kalkgranskog av högsta klass</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,19 +1190,117 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Billingens flora</t>
-        </is>
-      </c>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>67991210</v>
+      </c>
+      <c r="B7" t="n">
+        <v>89870</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>236437</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brun klibbskivling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Limacella glioderma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Maire</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stålkvarnebäcken väster om, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>425313</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6482378</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lerdala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-09-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kalkgranskog av högsta klass</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63699-2025 artfynd.xlsx
+++ b/artfynd/A 63699-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67991203</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67991200</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69847128</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69847108</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67991196</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,8 +1331,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67991210</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>